--- a/r5-core-64-adding-related-person/StructureDefinition-at-core-related-person.xlsx
+++ b/r5-core-64-adding-related-person/StructureDefinition-at-core-related-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3326" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3326" uniqueCount="496">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-related-person</t>
+    <t>https://fhir.hl7.at/core/r5/StructureDefinition/at-core-related-person</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T11:38:17+00:00</t>
+    <t>2026-10-13T17:05:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,7 +689,7 @@
     <t>RelatedPerson.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|5.0.0)
 </t>
   </si>
   <si>
@@ -1022,7 +1022,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|5.0.0</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1201,7 +1201,7 @@
     <t>RelatedPerson.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r5/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -1241,7 +1241,7 @@
     <t>The nature of the relationship between a patient and the related person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|5.0.0</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -1357,7 +1357,7 @@
     <t>AdministrativeGenderAddition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r5/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
 </t>
   </si>
   <si>
@@ -1399,7 +1399,7 @@
     <t>RelatedPerson.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-address}
+    <t xml:space="preserve">Address {https://fhir.hl7.at/core/r5/StructureDefinition/at-core-address}
 </t>
   </si>
   <si>
@@ -1410,6 +1410,10 @@
   </si>
   <si>
     <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>addr</t>
@@ -1868,7 +1872,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="98.24609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="85.5859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1883,7 +1887,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="58.23828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="46.8203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="20.2734375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -11362,27 +11366,27 @@
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>100</v>
+        <v>451</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11405,17 +11409,17 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11464,7 +11468,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11482,21 +11486,21 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11522,13 +11526,13 @@
         <v>209</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11578,7 +11582,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11593,10 +11597,10 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
@@ -11607,10 +11611,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11633,19 +11637,19 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -11694,7 +11698,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11712,10 +11716,10 @@
         <v>21</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
@@ -11723,10 +11727,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11835,10 +11839,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11949,14 +11953,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11978,10 +11982,10 @@
         <v>136</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>139</v>
@@ -12036,7 +12040,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12065,10 +12069,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12094,16 +12098,16 @@
         <v>180</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -12152,7 +12156,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>88</v>
@@ -12170,7 +12174,7 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>21</v>
@@ -12181,10 +12185,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12210,16 +12214,16 @@
         <v>285</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -12268,7 +12272,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12286,7 +12290,7 @@
         <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>21</v>

--- a/r5-core-64-adding-related-person/StructureDefinition-at-core-related-person.xlsx
+++ b/r5-core-64-adding-related-person/StructureDefinition-at-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T17:05:56+00:00</t>
+    <t>2026-10-13T17:36:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
